--- a/data/out/variants/v10_date_range_no_solar_lags/raw_v10_date_range_no_solar_lags.xlsx
+++ b/data/out/variants/v10_date_range_no_solar_lags/raw_v10_date_range_no_solar_lags.xlsx
@@ -526,19 +526,19 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>0.3187499440808549</v>
+        <v>0.3187499440808614</v>
       </c>
       <c r="G2" t="n">
-        <v>32.8561348098053</v>
+        <v>32.85613480980473</v>
       </c>
       <c r="H2" t="n">
-        <v>6571.859556615985</v>
+        <v>6571.859556615922</v>
       </c>
       <c r="I2" t="n">
-        <v>81.0670065847752</v>
+        <v>81.0670065847748</v>
       </c>
       <c r="J2" t="n">
-        <v>20.06473384517696</v>
+        <v>20.06473384517648</v>
       </c>
       <c r="K2" t="n">
         <v>13081</v>
@@ -550,7 +550,7 @@
         <v>2617</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05309629440307617</v>
+        <v>0.04508090019226074</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -580,19 +580,19 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.3191575632085752</v>
+        <v>0.3191485659290998</v>
       </c>
       <c r="G3" t="n">
-        <v>32.8650893995528</v>
+        <v>32.86637126685464</v>
       </c>
       <c r="H3" t="n">
-        <v>6567.927350465405</v>
+        <v>6568.01414511091</v>
       </c>
       <c r="I3" t="n">
-        <v>81.04275014130138</v>
+        <v>81.04328562633002</v>
       </c>
       <c r="J3" t="n">
-        <v>20.07986490512013</v>
+        <v>20.08133314442446</v>
       </c>
       <c r="K3" t="n">
         <v>13081</v>
@@ -604,7 +604,7 @@
         <v>2617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04051876068115234</v>
+        <v>0.03857707977294922</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -634,19 +634,19 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.354470215628099</v>
+        <v>0.3538570119011395</v>
       </c>
       <c r="G4" t="n">
-        <v>25.07821640932533</v>
+        <v>25.2679194497411</v>
       </c>
       <c r="H4" t="n">
-        <v>6227.274472338891</v>
+        <v>6233.189904914869</v>
       </c>
       <c r="I4" t="n">
-        <v>78.91308175669539</v>
+        <v>78.95055354406877</v>
       </c>
       <c r="J4" t="n">
-        <v>13.38181139394616</v>
+        <v>13.54661302777176</v>
       </c>
       <c r="K4" t="n">
         <v>13081</v>
@@ -658,7 +658,7 @@
         <v>2617</v>
       </c>
       <c r="N4" t="n">
-        <v>1.950400590896606</v>
+        <v>1.917895317077637</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3192586531359273</v>
+        <v>0.3192439296514199</v>
       </c>
       <c r="G5" t="n">
-        <v>32.85452767304649</v>
+        <v>32.85665476903265</v>
       </c>
       <c r="H5" t="n">
-        <v>6566.952159638815</v>
+        <v>6567.094193641638</v>
       </c>
       <c r="I5" t="n">
-        <v>81.03673339689117</v>
+        <v>81.03760974783029</v>
       </c>
       <c r="J5" t="n">
-        <v>20.07272976287571</v>
+        <v>20.07513845425161</v>
       </c>
       <c r="K5" t="n">
         <v>13081</v>
@@ -716,7 +716,7 @@
         <v>2617</v>
       </c>
       <c r="N5" t="n">
-        <v>19.38271546363831</v>
+        <v>19.23821687698364</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-120.2311372248381</v>
+        <v>-120.2297690982782</v>
       </c>
     </row>
     <row r="6">
@@ -748,14 +748,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 5}</t>
+          <t>{'max_depth': 5, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0.01434202972933596</v>
       </c>
       <c r="G6" t="n">
-        <v>67.59830700806995</v>
+        <v>67.59830700806994</v>
       </c>
       <c r="H6" t="n">
         <v>9508.41133178091</v>
@@ -776,7 +776,7 @@
         <v>2617</v>
       </c>
       <c r="N6" t="n">
-        <v>4.258209228515625</v>
+        <v>2.754607200622559</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-226.5779203529731</v>
+        <v>-226.4746248621063</v>
       </c>
     </row>
     <row r="7">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1393288951220225</v>
+        <v>0.1392913905038823</v>
       </c>
       <c r="G7" t="n">
-        <v>62.74503843031366</v>
+        <v>62.73934661231051</v>
       </c>
       <c r="H7" t="n">
-        <v>8302.692347032831</v>
+        <v>8303.054145290316</v>
       </c>
       <c r="I7" t="n">
-        <v>91.11911076735127</v>
+        <v>91.12109604965426</v>
       </c>
       <c r="J7" t="n">
-        <v>48.27885824174565</v>
+        <v>48.27403849716188</v>
       </c>
       <c r="K7" t="n">
         <v>13081</v>
@@ -836,7 +836,7 @@
         <v>2617</v>
       </c>
       <c r="N7" t="n">
-        <v>968.2557289600372</v>
+        <v>862.9306428432465</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-214.1897880477788</v>
+        <v>-214.1955890995829</v>
       </c>
     </row>
     <row r="8">
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.4594913460000679</v>
+        <v>0.459491346000068</v>
       </c>
       <c r="G8" t="n">
-        <v>39.05177938975331</v>
+        <v>39.0517793897533</v>
       </c>
       <c r="H8" t="n">
-        <v>5214.160251965816</v>
+        <v>5214.160251965815</v>
       </c>
       <c r="I8" t="n">
-        <v>72.2091424403158</v>
+        <v>72.20914244031579</v>
       </c>
       <c r="J8" t="n">
         <v>27.33355083458026</v>
@@ -896,7 +896,7 @@
         <v>2617</v>
       </c>
       <c r="N8" t="n">
-        <v>440.722550868988</v>
+        <v>396.0763924121857</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-226.1922977860644</v>
+        <v>-226.9316541178137</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-5.67668250477228</v>
+        <v>-5.531709103308541</v>
       </c>
       <c r="G9" t="n">
-        <v>234.7467273212093</v>
+        <v>231.9184182349415</v>
       </c>
       <c r="H9" t="n">
-        <v>64408.39064046432</v>
+        <v>63009.86622848589</v>
       </c>
       <c r="I9" t="n">
-        <v>253.7880821482055</v>
+        <v>251.0176611883831</v>
       </c>
       <c r="J9" t="n">
-        <v>201.3898081130964</v>
+        <v>199.1199358879489</v>
       </c>
       <c r="K9" t="n">
         <v>13081</v>
@@ -956,7 +956,7 @@
         <v>2617</v>
       </c>
       <c r="N9" t="n">
-        <v>40.12481880187988</v>
+        <v>32.51827645301819</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-470.8517386710223</v>
+        <v>-469.1319301308981</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-1.129740829570045</v>
+        <v>-1.189635092760811</v>
       </c>
       <c r="G10" t="n">
-        <v>114.2551711337955</v>
+        <v>115.7555330531142</v>
       </c>
       <c r="H10" t="n">
-        <v>20545.11042210663</v>
+        <v>21122.89633568816</v>
       </c>
       <c r="I10" t="n">
-        <v>143.3356564923977</v>
+        <v>145.3371815320779</v>
       </c>
       <c r="J10" t="n">
-        <v>93.57846052354526</v>
+        <v>95.01760997495384</v>
       </c>
       <c r="K10" t="n">
         <v>13081</v>
@@ -1016,7 +1016,7 @@
         <v>2617</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5407586097717285</v>
+        <v>0.5574769973754883</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-315.8014424434899</v>
+        <v>-318.1132484240939</v>
       </c>
     </row>
     <row r="11">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 538, 'learning_rate': 0.01646681866859615, 'max_depth': 3, 'subsample': 0.9582570659133056, 'colsample_bytree': 0.8691197975658852}</t>
+          <t>{'n_estimators': 562, 'learning_rate': 0.017779330045767507, 'max_depth': 3, 'subsample': 0.8479382913389394, 'colsample_bytree': 0.7868373837525601}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5023316719908076</v>
+        <v>0.4879053513305448</v>
       </c>
       <c r="G11" t="n">
-        <v>30.99414751950047</v>
+        <v>32.73504022104849</v>
       </c>
       <c r="H11" t="n">
-        <v>4800.8896719129</v>
+        <v>4940.057004780183</v>
       </c>
       <c r="I11" t="n">
-        <v>69.28845265924835</v>
+        <v>70.28553908721327</v>
       </c>
       <c r="J11" t="n">
-        <v>20.20699762093588</v>
+        <v>21.8797423818262</v>
       </c>
       <c r="K11" t="n">
         <v>13081</v>
@@ -1076,7 +1076,7 @@
         <v>2617</v>
       </c>
       <c r="N11" t="n">
-        <v>173.439389705658</v>
+        <v>121.911749124527</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 421, 'learning_rate': 0.012155808478487167, 'num_leaves': 47, 'min_child_samples': 20}</t>
+          <t>{'n_estimators': 738, 'learning_rate': 0.010010304642928692, 'num_leaves': 54, 'min_child_samples': 17}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.4936605795451244</v>
+        <v>0.4878167176498316</v>
       </c>
       <c r="G12" t="n">
-        <v>42.8140477694449</v>
+        <v>45.53992758581158</v>
       </c>
       <c r="H12" t="n">
-        <v>4884.537667623637</v>
+        <v>4940.912033116067</v>
       </c>
       <c r="I12" t="n">
-        <v>69.88946750135987</v>
+        <v>70.29162135785506</v>
       </c>
       <c r="J12" t="n">
-        <v>31.46511338966613</v>
+        <v>33.91052436895991</v>
       </c>
       <c r="K12" t="n">
         <v>13081</v>
@@ -1134,7 +1134,7 @@
         <v>2617</v>
       </c>
       <c r="N12" t="n">
-        <v>427.9489243030548</v>
+        <v>424.4486737251282</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 533, 'learning_rate': 0.03549705086771211, 'depth': 4}</t>
+          <t>{'iterations': 632, 'learning_rate': 0.019776144801648396, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.4875361933773371</v>
+        <v>0.4609182888652664</v>
       </c>
       <c r="G13" t="n">
-        <v>36.04692396984443</v>
+        <v>37.18495887358198</v>
       </c>
       <c r="H13" t="n">
-        <v>4943.618184998239</v>
+        <v>5200.394868720824</v>
       </c>
       <c r="I13" t="n">
-        <v>70.31086818549633</v>
+        <v>72.1137633792664</v>
       </c>
       <c r="J13" t="n">
-        <v>24.84385763650666</v>
+        <v>25.64740985256786</v>
       </c>
       <c r="K13" t="n">
         <v>13081</v>
@@ -1192,7 +1192,7 @@
         <v>2617</v>
       </c>
       <c r="N13" t="n">
-        <v>373.5432758331299</v>
+        <v>319.0169117450714</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{'max_depth': 20, 'min_samples_split': 2, 'n_estimators': 300}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.343094702061207</v>
+        <v>0.3581782082952614</v>
       </c>
       <c r="G14" t="n">
-        <v>56.85084830529738</v>
+        <v>54.09017890714562</v>
       </c>
       <c r="H14" t="n">
-        <v>6337.01138449977</v>
+        <v>6191.504336492552</v>
       </c>
       <c r="I14" t="n">
-        <v>79.6053477129506</v>
+        <v>78.68611272958242</v>
       </c>
       <c r="J14" t="n">
-        <v>43.47214571022619</v>
+        <v>40.76597085070789</v>
       </c>
       <c r="K14" t="n">
         <v>13081</v>
@@ -1250,7 +1250,7 @@
         <v>2617</v>
       </c>
       <c r="N14" t="n">
-        <v>164.6106050014496</v>
+        <v>143.0769944190979</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-223.5887243792937</v>
+        <v>-221.0164478856214</v>
       </c>
     </row>
     <row r="15">
@@ -1310,7 +1310,7 @@
         <v>2617</v>
       </c>
       <c r="N15" t="n">
-        <v>41.81564116477966</v>
+        <v>38.96607279777527</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1342,23 +1342,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (128, 64, 32), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.2907976232584094</v>
+        <v>0.4239232779497695</v>
       </c>
       <c r="G16" t="n">
-        <v>40.50142833415369</v>
+        <v>26.51195229803802</v>
       </c>
       <c r="H16" t="n">
-        <v>6841.509041603898</v>
+        <v>5557.277064795061</v>
       </c>
       <c r="I16" t="n">
-        <v>82.71341512477827</v>
+        <v>74.54714659056415</v>
       </c>
       <c r="J16" t="n">
-        <v>27.14653959606226</v>
+        <v>13.92923736181205</v>
       </c>
       <c r="K16" t="n">
         <v>13081</v>
@@ -1370,7 +1370,7 @@
         <v>2617</v>
       </c>
       <c r="N16" t="n">
-        <v>574.8933699131012</v>
+        <v>476.9195561408997</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-152.9866193830481</v>
+        <v>-147.2621506102097</v>
       </c>
     </row>
   </sheetData>
